--- a/data/seed/portfolio/L-2024-0197/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-0197/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J149"/>
+  <dimension ref="A1:J182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -542,35 +542,35 @@
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>7445000</v>
+        <v>12223000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Chust Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>254875872</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000600665421001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4381 01.07.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №35/26, НДС 12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>274645000</v>
+        <v>279423000</v>
       </c>
     </row>
     <row r="9">
@@ -580,63 +580,63 @@
       <c r="B9" t="n">
         <v>101</v>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>16368000</v>
-      </c>
-      <c r="D9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n">
+        <v>7976000</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tong Poligraf MChJ</t>
+          <t>Sarbon Metall MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>245530486</t>
+          <t>305591685</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000635949554001</t>
+          <t>20208000725275743001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9356</t>
+          <t>Предоплата за товар по договору №197/26 от 01.07.2026</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>258277000</v>
+        <v>287399000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>54026000</v>
+        <v>22786000</v>
       </c>
       <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oqtosh Tur Servis MChJ</t>
+          <t>Nihol Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>331587588</t>
+          <t>284659880</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000694569350001</t>
+          <t>20208000576757442001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -646,11 +646,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №197/26</t>
+          <t>Оплата за товары согласно с/ф №8101</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>204251000</v>
+        <v>264613000</v>
       </c>
     </row>
     <row r="11">
@@ -660,77 +660,77 @@
       <c r="B11" t="n">
         <v>103</v>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n">
-        <v>206114000</v>
-      </c>
+      <c r="C11" s="2" t="n">
+        <v>132084000</v>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Ishonch Sut AJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>380298299</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000132809358001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shartnoma №240/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за упаковочные материалы, с/ф №2016</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>410365000</v>
+        <v>132529000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>46625000</v>
+        <v>10719000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №6213 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №178/26, НДС 12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>456990000</v>
+        <v>143248000</v>
       </c>
     </row>
     <row r="13">
@@ -742,35 +742,35 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>15542000</v>
+        <v>37312000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saodat Polimer MChJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>336507613</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000945741401001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9803 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №254/26, НДС 12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>472532000</v>
+        <v>180560000</v>
       </c>
     </row>
     <row r="14">
@@ -780,37 +780,37 @@
       <c r="B14" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>32291000</v>
-      </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n">
+        <v>9690000</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Chust Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>254875872</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000600665421001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №70/26</t>
+          <t>Оплата за товар по с/ф №6280 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>440241000</v>
+        <v>190250000</v>
       </c>
     </row>
     <row r="15">
@@ -820,37 +820,37 @@
       <c r="B15" t="n">
         <v>107</v>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>49035000</v>
-      </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n">
+        <v>7885000</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nukus Meva Eksport XK</t>
+          <t>Ishonch Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>388059046</t>
+          <t>350761319</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000626356032001</t>
+          <t>20208000574140165001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №1238</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №20/26, НДС 12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>391206000</v>
+        <v>198135000</v>
       </c>
     </row>
     <row r="16">
@@ -860,58 +860,63 @@
       <c r="B16" t="n">
         <v>108</v>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>80073000</v>
-      </c>
-      <c r="D16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n">
+        <v>7815000</v>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ish haqi, reestr №4613</t>
+          <t>Предоплата за товар по договору №70/26 от 06.07.2026</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>311133000</v>
+        <v>205950000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n">
-        <v>11662000</v>
-      </c>
+      <c r="C17" s="2" t="n">
+        <v>30683000</v>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Andijon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>339388482</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000636920909001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -921,117 +926,117 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8633</t>
+          <t>Оплата за упаковочные материалы, с/ф №2704</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>322795000</v>
+        <v>175267000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>35252000</v>
+        <v>37614000</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Andijon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>339388482</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000636920909001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №129/26, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №9645</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>287543000</v>
+        <v>137653000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>7685000</v>
+        <v>61174000</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Guliston Qurilish AJ</t>
+          <t>Farovon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>200780196</t>
+          <t>211214499</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000974534353001</t>
+          <t>20208000282601608001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Ijara haqi iyul oyi uchun, shartnoma №32/23</t>
+          <t>Предоплата за материалы по договору №179/26</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>279858000</v>
+        <v>76479000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>20402000</v>
+        <v>69123000</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Nihol Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>290879699</t>
+          <t>284659880</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000674011958001</t>
+          <t>20208000576757442001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1041,232 +1046,232 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №241/26</t>
+          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №168/26</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>259456000</v>
+        <v>7356000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46213</v>
+        <v>46209</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>12511000</v>
+        <v>80073000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>318055916</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №121/26</t>
+          <t>Iyun oyi uchun ish haqi, reestr №3210</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>246945000</v>
+        <v>-72717000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46213</v>
+        <v>46210</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>12568000</v>
+        <v>7685000</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Qo'qon Meva-Sabzavot MChJ</t>
+          <t>Sarbon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>288160664</t>
+          <t>313219308</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000139414725001</t>
+          <t>20208000249747959001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1557</t>
+          <t>Аренда помещения за июль, дог. №37/24</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>234377000</v>
+        <v>-80402000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46213</v>
+        <v>46210</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>17420000</v>
+        <v>32599000</v>
       </c>
       <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Farovon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>211214499</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000282601608001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №144/26</t>
+          <t>Оплата за товары согласно с/ф №6175</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>216957000</v>
+        <v>-113001000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>75600000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>5413000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-0197)</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>16307000390946129417</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-0197 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата за товар по счет-фактуре №2828 от 08.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>141357000</v>
+        <v>-107588000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>31100000</v>
+        <v>21079000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bog'ishamol Yog'och AJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>201548758</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000286006654001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2543 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по с/ф №4878 за поставленный товар</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>172457000</v>
+        <v>-86509000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>26005000</v>
+        <v>7008000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Gulshan Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>270286648</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000749336604001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1276,37 +1281,37 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №169/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №148 от 09.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>198462000</v>
+        <v>-79501000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
-        <v>21829000</v>
-      </c>
+      <c r="C27" s="2" t="n">
+        <v>28128000</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Chirchiq Agro MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>311692015</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000914125098001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1316,157 +1321,152 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6975 13.07.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №86/26</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>220291000</v>
+        <v>-107629000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>16143000</v>
+        <v>41665000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saodat Polimer MChJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>336507613</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000945741401001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №41/26, QQS 12%</t>
+          <t>Предоплата за товар по дог. №121/26 от 10.07.2026</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>236434000</v>
+        <v>-65964000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>18800000</v>
-      </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n">
+        <v>29628000</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Chust Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>254875872</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000600665421001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №285/26</t>
+          <t>Оплата за продукцию по договору №268/26, НДС 12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>217634000</v>
+        <v>-36336000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>85107000</v>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n">
+        <v>14216000</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №41/26</t>
+          <t>Предоплата за товар по дог. №144/26 от 10.07.2026</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>132527000</v>
+        <v>-22120000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46217</v>
+        <v>46213</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n">
-        <v>11748000</v>
-      </c>
+      <c r="C31" s="2" t="n">
+        <v>75600000</v>
+      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>280886734</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-0197)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>16307000390946129417</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1476,37 +1476,37 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №2335 14.07.2026, QQS bilan</t>
+          <t>Kredit shartnomasi L-2024-0197 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>144275000</v>
+        <v>-97720000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n">
-        <v>9398000</v>
+        <v>20702000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Gulshan Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>270286648</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000749336604001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1516,37 +1516,37 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Shartnoma №205/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №4805 от 13.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>153673000</v>
+        <v>-77018000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>61991000</v>
+        <v>19560000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Gulshan Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>270286648</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000749336604001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1556,197 +1556,197 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6764 15.07.2026, QQS bilan</t>
+          <t>Shartnoma №218/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>215664000</v>
+        <v>-57458000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>34045000</v>
+        <v>8785000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bog'ishamol Yog'och AJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>201548758</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000286006654001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №267/26 от 15.07.2026</t>
+          <t>Оплата по счет-фактуре №599 за поставленный товар</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>249709000</v>
+        <v>-48673000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>10919000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>7707000</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Социальный налог за июнь 2026 г.</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №2468</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>238790000</v>
+        <v>-40966000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>10919000</v>
+        <v>122624000</v>
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Andijon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>339388482</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000636920909001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>JShDS iyun oyi uchun</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №220/26</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>227871000</v>
+        <v>-163590000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46220</v>
+        <v>46217</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n">
-        <v>6915000</v>
+        <v>5734000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mehnat Savdo MChJ</t>
+          <t>Ishonch Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>334320803</t>
+          <t>350761319</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000103522831001</t>
+          <t>20208000574140165001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №252/26, QQS 12%</t>
+          <t>Предоплата за товар по дог. №100/26 от 14.07.2026</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>234786000</v>
+        <v>-157856000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>10786000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>5732000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Qarshi Trans Servis MChJ</t>
+          <t>Durdona Polimer MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>347505037</t>
+          <t>232080301</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000122459997001</t>
+          <t>20208000352283124001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1756,117 +1756,117 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №27/26</t>
+          <t>Оплата за продукцию по дог. №263/26, НДС 12%</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>224000000</v>
+        <v>-152124000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46223</v>
+        <v>46219</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>53336000</v>
+        <v>10919000</v>
       </c>
       <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №163/26</t>
+          <t>Уплата социального налога за июнь</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>170664000</v>
+        <v>-163043000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46223</v>
+        <v>46219</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>56311000</v>
+        <v>10919000</v>
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №293/26</t>
+          <t>НДФЛ ЗА ИЮНЬ 2026</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>114353000</v>
+        <v>-173962000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46224</v>
+        <v>46220</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>9758000</v>
+        <v>174799000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Gulshan Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>270286648</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000749336604001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1876,357 +1876,357 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Shartnoma №250/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7865 17.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>124111000</v>
+        <v>837000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46225</v>
+        <v>46220</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>9535000</v>
+        <v>107396000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saodat Polimer MChJ</t>
+          <t>Gulshan Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>336507613</t>
+          <t>270286648</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000945741401001</t>
+          <t>20208000749336604001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2062 22.07.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №27/26 от 17.07.2026</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>133646000</v>
+        <v>108233000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46226</v>
+        <v>46223</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>13022000</v>
-      </c>
-      <c r="D43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n">
+        <v>48967000</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>QQS iyun 2026 uchun</t>
+          <t>Оплата по счет-фактуре №5640 за поставленный товар</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>120624000</v>
+        <v>157200000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46227</v>
+        <v>46223</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>13231000</v>
-      </c>
-      <c r="D44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n">
+        <v>10435000</v>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №35/26, QQS bilan</t>
+          <t>Предоплата за товар по дог. №163/26 от 20.07.2026</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>107393000</v>
+        <v>167635000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46230</v>
+        <v>46224</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>330976000</v>
+        <v>38422000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Chust Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>254875872</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000600665421001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРДУКЦИЮ ПО ДОГОВОРУ №14/26, НДС 12%</t>
+          <t>Оплата за товар по с/ф №7743 от 21.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>438369000</v>
+        <v>206057000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
-        <v>95726000</v>
+        <v>8050000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saodat Polimer MChJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>336507613</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000945741401001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9424 27.07.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №8896 за поставленный товар</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>534095000</v>
+        <v>214107000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>23899000</v>
-      </c>
+      <c r="C47" s="2" t="n">
+        <v>12833000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saodat Polimer MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>336507613</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000945741401001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SHARTNOMA №297/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Уплата налога на добавленную стоимость за июнь</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>557994000</v>
+        <v>201274000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n">
-        <v>19844000</v>
-      </c>
+      <c r="C48" s="2" t="n">
+        <v>33161000</v>
+      </c>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mehnat Savdo MChJ</t>
+          <t>Andijon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>334320803</t>
+          <t>339388482</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000103522831001</t>
+          <t>20208000636920909001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1524</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №52/26</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>577838000</v>
+        <v>168113000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>4803000</v>
+        <v>36767000</v>
       </c>
       <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Andijon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>339388482</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000254210054001</t>
+          <t>20208000636920909001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov iyul</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTN. №67/26</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>573035000</v>
+        <v>131346000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n">
-        <v>9216000</v>
-      </c>
-      <c r="D50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n">
+        <v>137208000</v>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Yangi Hayot Meva Eksport AJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>287969946</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000401195857001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2236,237 +2236,237 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №40/26</t>
+          <t>Оплата за товар по счет-фактуре №6607 от 24.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>563819000</v>
+        <v>268554000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>18046000</v>
-      </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n">
+        <v>12136000</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №12/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №8323 от 24.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>545773000</v>
+        <v>280690000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>316918000</v>
+        <v>4803000</v>
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000712740066001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №292/26, QQS bilan</t>
+          <t>Оплата за электроэнергию за июль 2026 г.</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>228855000</v>
+        <v>275887000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>49483000</v>
-      </c>
-      <c r="D53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n">
+        <v>38647000</v>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Gulshan Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>270286648</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000749336604001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №112/26</t>
+          <t>Оплата за продукцию по договору №286/26, НДС 12%</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>179372000</v>
+        <v>314534000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>35182000</v>
+        <v>17785000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saodat Polimer MChJ</t>
+          <t>Ishonch Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>336507613</t>
+          <t>350761319</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000945741401001</t>
+          <t>20208000574140165001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5608 30.07.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №34/26, НДС 12%</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>214554000</v>
+        <v>332319000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>30505000</v>
+        <v>11598000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Shartnoma №30/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по с/ф №6449 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>245059000</v>
+        <v>343917000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>16458000</v>
+        <v>9182000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mehnat Savdo MChJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>334320803</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000103522831001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2476,77 +2476,77 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Shartnoma №227/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №9462 за поставленный товар</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>261517000</v>
+        <v>353099000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
       <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="n">
-        <v>6736000</v>
+        <v>8746000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7117</t>
+          <t>Оплата за товар по с/ф №1431 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>268253000</v>
+        <v>361845000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>20306000</v>
+        <v>23425000</v>
       </c>
       <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Nihol Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>290879699</t>
+          <t>284659880</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000674011958001</t>
+          <t>20208000576757442001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2556,32 +2556,37 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №89/26</t>
+          <t>Предоплата за материалы по договору №184/26</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>247947000</v>
+        <v>338420000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>300000</v>
+        <v>142533000</v>
       </c>
       <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Andijon Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>339388482</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000636920909001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2591,237 +2596,232 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Оплата за сырье по дог. №54/26 от 27.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>247647000</v>
+        <v>195887000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>46214000</v>
-      </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n">
+        <v>54109000</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №75/26</t>
+          <t>Оплата по с/ф №7874 за поставленный товар</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>201433000</v>
+        <v>249996000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n">
-        <v>51060000</v>
-      </c>
-      <c r="D61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n">
+        <v>21889000</v>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Gulshan Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>270286648</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000749336604001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5323</t>
+          <t>Оплата по счет-фактуре №2479 за поставленный товар</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>150373000</v>
+        <v>271885000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>176608000</v>
+        <v>24609000</v>
       </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Tong Poligraf MChJ</t>
+          <t>Farovon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>245530486</t>
+          <t>211214499</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000635949554001</t>
+          <t>20208000282601608001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №219/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №8227</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>-26235000</v>
+        <v>247276000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46237</v>
+        <v>46233</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
-      <c r="C63" s="2" t="n">
-        <v>180161000</v>
-      </c>
-      <c r="D63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n">
+        <v>61462000</v>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oqtosh Tur Servis MChJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>331587588</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000694569350001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №36/26, QQS bilan</t>
+          <t>Предоплата за товар по договору №89/26 от 30.07.2026</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>-206396000</v>
+        <v>308738000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46238</v>
+        <v>46234</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>23900000</v>
+        <v>27704000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saodat Polimer MChJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>336507613</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000945741401001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №153/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №69/26 от 31.07.2026</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>-182496000</v>
+        <v>336442000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46239</v>
+        <v>46234</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
-      <c r="C65" s="2" t="n"/>
-      <c r="D65" s="2" t="n">
-        <v>16306000</v>
-      </c>
+      <c r="C65" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lazzat Avto Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>341702866</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000847493366001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2831,32 +2831,37 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4909</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>-166190000</v>
+        <v>336142000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46239</v>
+        <v>46234</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>78991000</v>
+        <v>74552000</v>
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Andijon Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>339388482</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000636920909001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2866,77 +2871,77 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ish haqi, reestr №4378</t>
+          <t>Оплата за транспортные услуги по договору №226/26</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>-245181000</v>
+        <v>261590000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46240</v>
+        <v>46237</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n">
-        <v>70263000</v>
+        <v>15487000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8585 06.08.2026, QQS bilan</t>
+          <t>ОПЛАТА ПО С/Ф №2913 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>-174918000</v>
+        <v>277077000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46240</v>
+        <v>46237</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="n">
-        <v>16341000</v>
-      </c>
+      <c r="C68" s="2" t="n">
+        <v>4256000</v>
+      </c>
+      <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Mehnat Savdo MChJ</t>
+          <t>Andijon Logistik MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>334320803</t>
+          <t>328624429</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000103522831001</t>
+          <t>20208000327041674001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2946,117 +2951,112 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1789 за поставленный товар</t>
+          <t>Оплата за сырье по дог. №133/26 от 03.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>-158577000</v>
+        <v>272821000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46240</v>
+        <v>46237</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>30084000</v>
+        <v>5219000</v>
       </c>
       <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Qarshi Trans Servis MChJ</t>
+          <t>Nihol Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>347505037</t>
+          <t>284659880</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000122459997001</t>
+          <t>20208000576757442001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №61/26, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №33/26, QQS bilan</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>-188661000</v>
+        <v>267602000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46241</v>
+        <v>46237</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n">
-        <v>62044000</v>
-      </c>
+      <c r="C70" s="2" t="n">
+        <v>11640000</v>
+      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lazzat Avto Savdo MChJ</t>
+          <t>Farovon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>341702866</t>
+          <t>211214499</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000847493366001</t>
+          <t>20208000282601608001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9542 от 07.08.2026, в т.ч. НДС 12%</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №7165</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>-126617000</v>
+        <v>255962000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
-      <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="n">
-        <v>11124000</v>
-      </c>
+      <c r="C71" s="2" t="n">
+        <v>78991000</v>
+      </c>
+      <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>280886734</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3066,37 +3066,37 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №5692 07.08.2026, QQS bilan</t>
+          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>-115493000</v>
+        <v>176971000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46244</v>
+        <v>46239</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n">
-        <v>36431000</v>
+        <v>10189000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Gulshan Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>270286648</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000749336604001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3106,37 +3106,37 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Shartnoma №177/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1938</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>-79062000</v>
+        <v>187160000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46244</v>
+        <v>46240</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n">
-        <v>12781000</v>
-      </c>
+      <c r="C73" s="2" t="n">
+        <v>10225000</v>
+      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Nihol Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>284659880</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000576757442001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3146,51 +3146,51 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Shartnoma №135/26 bo'yicha oldindan to'lov</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №207/26, QQS bilan</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>-66281000</v>
+        <v>176935000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>7581000</v>
-      </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n">
+        <v>10099000</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Guliston Qurilish AJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>200780196</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000974534353001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Ijara haqi avgust oyi uchun, shartnma №32/23</t>
+          <t>Shartnoma №95/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>-73862000</v>
+        <v>187034000</v>
       </c>
     </row>
     <row r="75">
@@ -3200,37 +3200,37 @@
       <c r="B75" t="n">
         <v>167</v>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>24495000</v>
-      </c>
-      <c r="D75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n">
+        <v>249372000</v>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №124/26, QQS bilan</t>
+          <t>Оплата по счет-фактуре №2434 за поставленный товар</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>-98357000</v>
+        <v>436406000</v>
       </c>
     </row>
     <row r="76">
@@ -3240,98 +3240,98 @@
       <c r="B76" t="n">
         <v>168</v>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>75600000</v>
-      </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n">
+        <v>37119000</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-0197)</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>16307000390946129417</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-0197 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата за товар по счет-фактуре №6643 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>-173957000</v>
+        <v>473525000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>13230000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>7581000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Sarbon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>313219308</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000249747959001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Shartnoma №165/26 bo'yicha oldindan to'lov</t>
+          <t>Арендная плата за август 2026 г. по дог. №37/24</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>-160727000</v>
+        <v>465944000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
-      <c r="C78" s="2" t="n"/>
-      <c r="D78" s="2" t="n">
-        <v>21067000</v>
-      </c>
+      <c r="C78" s="2" t="n">
+        <v>75600000</v>
+      </c>
+      <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>280886734</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-0197)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>16307000390946129417</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3341,131 +3341,131 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №70/26, НДС 12%</t>
+          <t>Kredit shartnomasi L-2024-0197 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>-139660000</v>
+        <v>390344000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>14877000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>8180000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saodat Polimer MChJ</t>
+          <t>Chirchiq Agro MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>336507613</t>
+          <t>311692015</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000945741401001</t>
+          <t>20208000914125098001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8530 13.08.2026, QQS bilan</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №7186</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>-124783000</v>
+        <v>382164000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
-      <c r="C80" s="2" t="n">
-        <v>9466000</v>
-      </c>
-      <c r="D80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n">
+        <v>11005000</v>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №275/26, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2413</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>-134249000</v>
+        <v>393169000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>10772000</v>
-      </c>
-      <c r="D81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n">
+        <v>15308000</v>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ijtimoiy soliq</t>
+          <t>Предоплата за товар по договору №244/26 от 13.08.2026</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>-145021000</v>
+        <v>408477000</v>
       </c>
     </row>
     <row r="82">
@@ -3475,143 +3475,143 @@
       <c r="B82" t="n">
         <v>174</v>
       </c>
-      <c r="C82" s="2" t="n">
-        <v>10772000</v>
-      </c>
-      <c r="D82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n">
+        <v>8560000</v>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ishonch Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>350761319</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000574140165001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>JShDS iyul oyi uchun</t>
+          <t>Предоплата за товар по договору №25/26 от 14.08.2026</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>-155793000</v>
+        <v>417037000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n">
-        <v>15355000</v>
-      </c>
+      <c r="C83" s="2" t="n">
+        <v>10772000</v>
+      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saodat Polimer MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>336507613</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000945741401001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №244/26 от 17.08.2026</t>
+          <t>Iyul oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>-140438000</v>
+        <v>406265000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>13821000</v>
+        <v>10772000</v>
       </c>
       <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTN. №227/26, QQS BILAN</t>
+          <t>НДФЛ за июль 2026</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>-154259000</v>
+        <v>395493000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>219532000</v>
+        <v>32348000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Gulshan Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>270286648</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000749336604001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3621,117 +3621,117 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Shartnoma №79/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №528</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>65273000</v>
+        <v>427841000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>143203000</v>
+        <v>22008000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №142/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №280/26, НДС 12%</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>208476000</v>
+        <v>449849000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n">
-        <v>67218000</v>
+        <v>13922000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bog'ishamol Yog'och AJ</t>
+          <t>Ishonch Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>201548758</t>
+          <t>350761319</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000286006654001</t>
+          <t>20208000574140165001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №99/26 от 18.08.2026</t>
+          <t>Оплата за продукцию по договору №133/26, НДС 12%</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>275694000</v>
+        <v>463771000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>19341000</v>
-      </c>
+      <c r="C88" s="2" t="n">
+        <v>10655000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Andijon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>339388482</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000636920909001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3741,77 +3741,77 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №67/26, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №5609</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>295035000</v>
+        <v>453116000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>28674000</v>
+        <v>14755000</v>
       </c>
       <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Nihol Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>284659880</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000576757442001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №1/26</t>
+          <t>Оплата за сырье по договору №268/26 от 17.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>266361000</v>
+        <v>438361000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n">
-        <v>58656000</v>
-      </c>
+      <c r="C90" s="2" t="n">
+        <v>50503000</v>
+      </c>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Nihol Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>284659880</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000576757442001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3821,117 +3821,117 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5357</t>
+          <t>Оплата за транспортные услуги по договору №137/26</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>325017000</v>
+        <v>387858000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n">
-        <v>21796000</v>
-      </c>
+      <c r="C91" s="2" t="n">
+        <v>51440000</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Lazzat Avto Savdo MChJ</t>
+          <t>Farovon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>341702866</t>
+          <t>211214499</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000847493366001</t>
+          <t>20208000282601608001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5684</t>
+          <t>Оплата за упаковочные материалы, с/ф №9019</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>346813000</v>
+        <v>336418000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
       <c r="C92" s="2" t="n"/>
       <c r="D92" s="2" t="n">
-        <v>61202000</v>
+        <v>48134000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bog'ishamol Yog'och AJ</t>
+          <t>Gulshan Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>201548758</t>
+          <t>270286648</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000286006654001</t>
+          <t>20208000749336604001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4625 20.08.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №263 от 19.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>408015000</v>
+        <v>384552000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46255</v>
+        <v>46253</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>59218000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>13350000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Andijon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>339388482</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000636920909001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3941,37 +3941,37 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №186/26, НДС 12%</t>
+          <t>Предоплата за материалы по договору №297/26</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>467233000</v>
+        <v>371202000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>50494000</v>
+        <v>9301000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Gulshan Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>270286648</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000749336604001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -3981,37 +3981,37 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9872 24.08.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №876 за поставленный товар</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>517727000</v>
+        <v>380503000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n">
-        <v>31069000</v>
-      </c>
+      <c r="C95" s="2" t="n">
+        <v>44677000</v>
+      </c>
+      <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Lazzat Avto Savdo MChJ</t>
+          <t>Nihol Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>341702866</t>
+          <t>284659880</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000847493366001</t>
+          <t>20208000576757442001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4021,91 +4021,91 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №165/26, QQS 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №121/26</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>548796000</v>
+        <v>335826000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>4738000</v>
+        <v>58685000</v>
       </c>
       <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Andijon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>339388482</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000254210054001</t>
+          <t>20208000636920909001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Оплата за товары согласно с/ф №7305</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>544058000</v>
+        <v>277141000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>13097000</v>
-      </c>
-      <c r="D97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n">
+        <v>37274000</v>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>QQS iyul 2026 uchun</t>
+          <t>Оплата за продукцию по договору №124/26, НДС 12%</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>530961000</v>
+        <v>314415000</v>
       </c>
     </row>
     <row r="98">
@@ -4115,298 +4115,303 @@
       <c r="B98" t="n">
         <v>190</v>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>244366000</v>
-      </c>
-      <c r="D98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n">
+        <v>18950000</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Ishonch Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>350761319</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000574140165001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №35/26 от 24.08.2026, НДС 12%</t>
+          <t>Предоплата за товар по договору №160/26 от 24.08.2026</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>286595000</v>
+        <v>333365000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>27177000</v>
+        <v>12405000</v>
       </c>
       <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №172/26, QQS bilan</t>
+          <t>НДС за июль 2026 г.</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>259418000</v>
+        <v>320960000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n">
-        <v>28806000</v>
-      </c>
+      <c r="C100" s="2" t="n">
+        <v>4647000</v>
+      </c>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Mehnat Savdo MChJ</t>
+          <t>Andijon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>334320803</t>
+          <t>339388482</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000103522831001</t>
+          <t>20208000636920909001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8602</t>
+          <t>Оплата за сырье по дог. №186/26 от 25.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>288224000</v>
+        <v>316313000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46261</v>
+        <v>46259</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>10288000</v>
+        <v>8950000</v>
       </c>
       <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Qo'qon Meva-Sabzavot MChJ</t>
+          <t>Nihol Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>288160664</t>
+          <t>284659880</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000139414725001</t>
+          <t>20208000576757442001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №252/26</t>
+          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №281/26</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>277936000</v>
+        <v>307363000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46262</v>
+        <v>46260</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
-      <c r="C102" s="2" t="n">
-        <v>18464000</v>
-      </c>
-      <c r="D102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n">
+        <v>25872000</v>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Ishonch Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>350761319</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000574140165001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8156</t>
+          <t>Оплата по счет-фактуре №422 за поставленный товар</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>259472000</v>
+        <v>333235000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n">
-        <v>17171000</v>
-      </c>
+      <c r="C103" s="2" t="n">
+        <v>4427000</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Farovon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>211214499</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000282601608001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №254/26 от 31.08.2026</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №170/26</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>276643000</v>
+        <v>328808000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>300000</v>
+        <v>4738000</v>
       </c>
       <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000712740066001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>276343000</v>
+        <v>324070000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>14589000</v>
+        <v>7873000</v>
       </c>
       <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Oqtosh Tur Servis MChJ</t>
+          <t>Andijon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>331587588</t>
+          <t>339388482</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000694569350001</t>
+          <t>20208000636920909001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4416,77 +4421,77 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №127/26</t>
+          <t>Tovarlar uchun to'lov h/f №9183</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>261754000</v>
+        <v>316197000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46266</v>
+        <v>46261</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
       <c r="C106" s="2" t="n"/>
       <c r="D106" s="2" t="n">
-        <v>151910000</v>
+        <v>9026000</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Mehnat Savdo MChJ</t>
+          <t>Bog'ishamol Qog'oz AJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>334320803</t>
+          <t>204770671</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000103522831001</t>
+          <t>20208000661487246001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>SHARTNOMA №236/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>ОПЛАА ПО СЧЕТ-ФАКТУРЕ №9025 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>413664000</v>
+        <v>325223000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46267</v>
+        <v>46261</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n">
-        <v>26000000</v>
-      </c>
+      <c r="C107" s="2" t="n">
+        <v>11880000</v>
+      </c>
+      <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Nihol Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>284659880</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000576757442001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4496,182 +4501,182 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4714 от 02.09.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за материалы по договору №5/26</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>439664000</v>
+        <v>313343000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46267</v>
+        <v>46262</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
-      <c r="C108" s="2" t="n">
-        <v>17121000</v>
-      </c>
-      <c r="D108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n">
+        <v>429870000</v>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №268/26</t>
+          <t>Оплата за товар по с/ф №7534 от 28.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>422543000</v>
+        <v>743213000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46272</v>
+        <v>46262</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n"/>
-      <c r="D109" s="2" t="n">
-        <v>13810000</v>
-      </c>
+      <c r="C109" s="2" t="n">
+        <v>9511000</v>
+      </c>
+      <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Saodat Polimer MChJ</t>
+          <t>Farovon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>336507613</t>
+          <t>211214499</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000945741401001</t>
+          <t>20208000282601608001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5127 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №83/26, QQS bilan</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>436353000</v>
+        <v>733702000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
-      <c r="C110" s="2" t="n">
-        <v>7813000</v>
-      </c>
-      <c r="D110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n">
+        <v>15395000</v>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Guliston Qurilish AJ</t>
+          <t>Ishonch Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>200780196</t>
+          <t>350761319</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000974534353001</t>
+          <t>20208000574140165001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Аренда помещения за сентябрь, дог. №32/23</t>
+          <t>Оплата за товар по счет-фактуре №7096 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>428540000</v>
+        <v>749097000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>27951000</v>
-      </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n">
+        <v>14504000</v>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №7/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №224/26, НДС 12%</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>400589000</v>
+        <v>763601000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>81408000</v>
+        <v>300000</v>
       </c>
       <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
@@ -4691,77 +4696,77 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ish haqi, reestr №5654</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за август</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>319181000</v>
+        <v>763301000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46273</v>
+        <v>46265</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>50531000</v>
+        <v>5411000</v>
       </c>
       <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Nihol Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>284659880</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000576757442001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №15/26 от 08.09.2026, НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №14/26, QQS bilan</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>268650000</v>
+        <v>757890000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>114255000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>40610000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Andijon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>339388482</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000636920909001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4771,232 +4776,237 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №15/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №273/26</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>382905000</v>
+        <v>717280000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46275</v>
+        <v>46265</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>15076000</v>
-      </c>
+      <c r="C115" s="2" t="n">
+        <v>469876000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bog'ishamol Yog'och AJ</t>
+          <t>Andijon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>201548758</t>
+          <t>339388482</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000286006654001</t>
+          <t>20208000636920909001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>SHARTNOMA №244/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за сырье по договору №54/26 от 31.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>397981000</v>
+        <v>247404000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46275</v>
+        <v>46266</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
-      <c r="C116" s="2" t="n">
-        <v>47138000</v>
-      </c>
-      <c r="D116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n">
+        <v>42163000</v>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Durdona Polimer MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>290879699</t>
+          <t>232080301</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000674011958001</t>
+          <t>20208000352283124001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №211/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №34/26, НДС 12%</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>350843000</v>
+        <v>289567000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46275</v>
+        <v>46267</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
-      <c r="C117" s="2" t="n">
-        <v>75600000</v>
-      </c>
-      <c r="D117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n">
+        <v>14924000</v>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-0197)</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>16307000390946129417</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-0197 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата по с/ф №7017 за поставленный товар</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>275243000</v>
+        <v>304491000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46276</v>
+        <v>46267</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n">
-        <v>46987000</v>
-      </c>
+      <c r="C118" s="2" t="n">
+        <v>58584000</v>
+      </c>
+      <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Saodat Polimer MChJ</t>
+          <t>Andijon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>336507613</t>
+          <t>339388482</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000945741401001</t>
+          <t>20208000636920909001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2849 11.09.2026, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №5984</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>322230000</v>
+        <v>245907000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46276</v>
+        <v>46268</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
-      <c r="C119" s="2" t="n">
-        <v>20458000</v>
-      </c>
-      <c r="D119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n">
+        <v>15586000</v>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №201/26</t>
+          <t>Оплата за товар по счет-фактуре №9221 от 03.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>301772000</v>
+        <v>261493000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46279</v>
+        <v>46268</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>64681000</v>
+        <v>12459000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mehnat Savdo MChJ</t>
+          <t>Durdona Polimer MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>334320803</t>
+          <t>232080301</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000103522831001</t>
+          <t>20208000352283124001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5006,117 +5016,117 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1904</t>
+          <t>Mahsulot uchun to'lov, shartnoma №191/26, QQS 12%</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>366453000</v>
+        <v>273952000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46279</v>
+        <v>46268</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n">
-        <v>24566000</v>
-      </c>
+      <c r="C121" s="2" t="n">
+        <v>82203000</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mehnat Savdo MChJ</t>
+          <t>Andijon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>334320803</t>
+          <t>339388482</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000103522831001</t>
+          <t>20208000636920909001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №234 от 14.09.2026, в т.ч. НДС 12%</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №121/26 ОТ 03.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>391019000</v>
+        <v>191749000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46279</v>
+        <v>46269</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>29996000</v>
-      </c>
-      <c r="D122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n">
+        <v>36713000</v>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6258</t>
+          <t>Оплата по с/ф №4868 за поставленный товар</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>361023000</v>
+        <v>228462000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46280</v>
+        <v>46269</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
       <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="n">
-        <v>53721000</v>
+        <v>12115000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mehnat Savdo MChJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>334320803</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000103522831001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5126,77 +5136,77 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Shartnoma №239/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по с/ф №9068 за поставленный товар</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>414744000</v>
+        <v>240577000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46281</v>
+        <v>46269</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" s="2" t="n">
-        <v>47866000</v>
-      </c>
+      <c r="C124" s="2" t="n">
+        <v>45263000</v>
+      </c>
+      <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Farovon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>211214499</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000282601608001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №80/26, QQS 12%</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №2374</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>462610000</v>
+        <v>195314000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46281</v>
+        <v>46272</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="n">
-        <v>29078000</v>
+        <v>39805000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Gulshan Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>270286648</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000749336604001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5206,157 +5216,157 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Shartnoma №176/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №3915 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>491688000</v>
+        <v>235119000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46281</v>
+        <v>46272</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
       <c r="C126" s="2" t="n"/>
       <c r="D126" s="2" t="n">
-        <v>25058000</v>
+        <v>23022000</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9482</t>
+          <t>Предоплата за товар по договору №218/26 от 07.09.2026</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>516746000</v>
+        <v>258141000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46281</v>
+        <v>46272</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
-      <c r="C127" s="2" t="n">
-        <v>11101000</v>
-      </c>
-      <c r="D127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n">
+        <v>17195000</v>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Уплата социального налога за август</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №400</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>505645000</v>
+        <v>275336000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46281</v>
+        <v>46272</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
-      <c r="C128" s="2" t="n">
-        <v>11101000</v>
-      </c>
-      <c r="D128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n">
+        <v>16998000</v>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Sarbon Metall MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>305591685</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000725275743001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>JShDS avgust oyi uchun</t>
+          <t>Предоплата за товар по дог. №48/26 от 07.09.2026</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>494544000</v>
+        <v>292334000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46286</v>
+        <v>46272</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="n">
-        <v>38525000</v>
+        <v>15969000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mehnat Savdo MChJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>334320803</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000103522831001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5366,237 +5376,232 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Shartnoma №141/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №7824 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>533069000</v>
+        <v>308303000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46286</v>
+        <v>46272</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>29285000</v>
+        <v>15349000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7198</t>
+          <t>Предоплата за товар по договору №5/26 от 07.09.2026</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>562354000</v>
+        <v>323652000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46286</v>
+        <v>46272</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n">
-        <v>28036000</v>
+        <v>10297000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №197/26, QQS 12%</t>
+          <t>Shartnoma №53/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>590390000</v>
+        <v>333949000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46286</v>
+        <v>46272</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>14363000</v>
+        <v>8602000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Saodat Polimer MChJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>336507613</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000945741401001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1898 за поставленный товар</t>
+          <t>Предоплата за товар по договору №233/26 от 07.09.2026</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>604753000</v>
+        <v>342551000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46286</v>
+        <v>46272</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n">
-        <v>13231000</v>
-      </c>
-      <c r="D133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n">
+        <v>5743000</v>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ishonch Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>350761319</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000574140165001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>НДС за август 2026 г.</t>
+          <t>Оплата по с/ф №7657 за поставленный товар</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>591522000</v>
+        <v>348294000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46288</v>
+        <v>46272</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>19337000</v>
+        <v>7813000</v>
       </c>
       <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Sarbon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>313219308</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000249747959001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №88/26</t>
+          <t>Арендная плата за сентябрь 2026 г. по договору №37/24</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>572185000</v>
+        <v>340481000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46289</v>
+        <v>46272</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>96546000</v>
-      </c>
+      <c r="C135" s="2" t="n">
+        <v>81408000</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>280886734</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5606,117 +5611,117 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №1115 24.09.2026, QQS bilan</t>
+          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>668731000</v>
+        <v>259073000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46289</v>
+        <v>46273</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
       <c r="C136" s="2" t="n"/>
       <c r="D136" s="2" t="n">
-        <v>44813000</v>
+        <v>40257000</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Saodat Polimer MChJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>336507613</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000945741401001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №3995</t>
+          <t>Оплата за продукцию по договору №167/26, НДС 12%</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>713544000</v>
+        <v>299330000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46289</v>
+        <v>46274</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>4883000</v>
+        <v>21208000</v>
       </c>
       <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Farovon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>211214499</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000254210054001</t>
+          <t>20208000282601608001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Оплата за упаковочные материалы, с/ф №7555</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>708661000</v>
+        <v>278122000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46290</v>
+        <v>46274</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
-      <c r="C138" s="2" t="n"/>
-      <c r="D138" s="2" t="n">
-        <v>70667000</v>
-      </c>
+      <c r="C138" s="2" t="n">
+        <v>85971000</v>
+      </c>
+      <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Andijon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>339388482</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000636920909001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5726,37 +5731,37 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №217/26, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №6173</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>779328000</v>
+        <v>192151000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46293</v>
+        <v>46275</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>66724000</v>
+        <v>47361000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Mehnat Savdo MChJ</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>334320803</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000103522831001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5766,37 +5771,37 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7259 от 28.09.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по дог. №234/26 от 10.09.2026</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>846052000</v>
+        <v>239512000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46293</v>
+        <v>46275</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>53827000</v>
+        <v>10619000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Saodat Qurilish MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>353048646</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000594955458001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5806,117 +5811,112 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2503 28.09.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №209/26, НДС 12%</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>899879000</v>
+        <v>250131000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46293</v>
+        <v>46275</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
-      <c r="C141" s="2" t="n"/>
-      <c r="D141" s="2" t="n">
-        <v>20506000</v>
-      </c>
+      <c r="C141" s="2" t="n">
+        <v>22815000</v>
+      </c>
+      <c r="D141" s="2" t="n"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Saodat Polimer MChJ</t>
+          <t>Andijon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>336507613</t>
+          <t>339388482</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000945741401001</t>
+          <t>20208000636920909001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3127 от 28.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №8949</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>920385000</v>
+        <v>227316000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46293</v>
+        <v>46275</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>26156000</v>
+        <v>75600000</v>
       </c>
       <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>318055916</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-0197)</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>16307000390946129417</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №235/26</t>
+          <t>Kredit shartnomasi L-2024-0197 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>894229000</v>
+        <v>151716000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46293</v>
+        <v>46276</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
-      <c r="C143" s="2" t="n">
-        <v>37225000</v>
-      </c>
-      <c r="D143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n">
+        <v>13186000</v>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Yulduz Polimer MChJ</t>
+          <t>Ishonch Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>290879699</t>
+          <t>350761319</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000674011958001</t>
+          <t>20208000574140165001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5926,191 +5926,1511 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Materiallar uchunoldindan to'lov, shartnoma №55/26</t>
+          <t>Оплата по счет-фактуре №1535 за поставленный товар</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>857004000</v>
+        <v>164902000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46293</v>
+        <v>46276</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
       <c r="C144" s="2" t="n">
-        <v>55513000</v>
+        <v>69933000</v>
       </c>
       <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Andijon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>339388482</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000636920909001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №128/26, QQS bilan</t>
+          <t>Оплата за сырье по договору №44/26 от 11.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>801491000</v>
+        <v>94969000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46293</v>
+        <v>46279</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n">
-        <v>570482000</v>
-      </c>
-      <c r="D145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n">
+        <v>176390000</v>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Sarbon Sut MChJ</t>
+          <t>Ishonch Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>318055916</t>
+          <t>350761319</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000517252757001</t>
+          <t>20208000574140165001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №202/26</t>
+          <t>Оплата за товар по счет-фактуре №6473 от 14.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>231009000</v>
+        <v>271359000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46294</v>
+        <v>46279</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
       <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="n">
-        <v>26291000</v>
+        <v>24862000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Toshkent Mehmonxona XK</t>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>280886734</t>
+          <t>288673440</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000018452864001</t>
+          <t>20208000845286443001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №2351 за поставленный товар</t>
+          <t>Предоплата за товар по договору №136/26 от 14.09.2026</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>257300000</v>
+        <v>296221000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46295</v>
+        <v>46279</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
-      <c r="C147" s="2" t="n">
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n">
+        <v>22978000</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>288673440</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>20208000845286443001</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №18/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>319199000</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B148" t="n">
+        <v>240</v>
+      </c>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="2" t="n">
+        <v>14602000</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>288673440</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>20208000845286443001</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №232/26 от 14.09.2026</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>333801000</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B149" t="n">
+        <v>241</v>
+      </c>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n">
+        <v>14112000</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>288673440</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>20208000845286443001</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Shartnoma №279/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>347913000</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B150" t="n">
+        <v>242</v>
+      </c>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n">
+        <v>6357000</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Ishonch Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>350761319</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>20208000574140165001</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №79/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>354270000</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B151" t="n">
+        <v>243</v>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v>11101000</v>
+      </c>
+      <c r="D151" s="2" t="n"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Уплата социального налога за август</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>343169000</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B152" t="n">
+        <v>244</v>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v>11101000</v>
+      </c>
+      <c r="D152" s="2" t="n"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Налог на доходы физических лиц за август 2026 г.</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>332068000</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B153" t="n">
+        <v>245</v>
+      </c>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n">
+        <v>48561000</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Sarbon Metall MChJ</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>305591685</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>20208000725275743001</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по дог. №250/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>380629000</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B154" t="n">
+        <v>246</v>
+      </c>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n">
+        <v>36485000</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>288673440</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>20208000845286443001</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по дог. №48/26 от 15.09.2026</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>417114000</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B155" t="n">
+        <v>247</v>
+      </c>
+      <c r="C155" s="2" t="n"/>
+      <c r="D155" s="2" t="n">
+        <v>15728000</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>288673440</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>20208000845286443001</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №6454</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>432842000</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B156" t="n">
+        <v>248</v>
+      </c>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n">
+        <v>119065000</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>288673440</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>20208000845286443001</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №5772 от 16.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>551907000</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B157" t="n">
+        <v>249</v>
+      </c>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n">
+        <v>21260000</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>288673440</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>20208000845286443001</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №6431 от 16.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>573167000</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B158" t="n">
+        <v>250</v>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v>75287000</v>
+      </c>
+      <c r="D158" s="2" t="n"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Nihol Un Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>284659880</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>20208000576757442001</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Оплата за упаковочные материалы, с/ф №1953</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>497880000</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B159" t="n">
+        <v>251</v>
+      </c>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>8602000</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>288673440</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>20208000845286443001</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по дог. №71/26 от 17.09.2026</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>506482000</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B160" t="n">
+        <v>252</v>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>47231000</v>
+      </c>
+      <c r="D160" s="2" t="n"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Farovon Farm Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>211214499</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>20208000282601608001</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun to'lov, shartn. №235/26, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>459251000</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B161" t="n">
+        <v>253</v>
+      </c>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n">
+        <v>6298000</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>288673440</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>20208000845286443001</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Оплата за товар по с/ф №225 от 18.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>465549000</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B162" t="n">
+        <v>254</v>
+      </c>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="2" t="n">
+        <v>51095000</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>288673440</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>20208000845286443001</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №9553 21.09.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>516644000</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B163" t="n">
+        <v>255</v>
+      </c>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n">
+        <v>15663000</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Ishonch Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>350761319</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20208000574140165001</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по дог. №170/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>532307000</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B164" t="n">
+        <v>256</v>
+      </c>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n">
+        <v>9278000</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>288673440</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>20208000845286443001</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Shartnoma №163/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>541585000</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B165" t="n">
+        <v>257</v>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>15311000</v>
+      </c>
+      <c r="D165" s="2" t="n"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Andijon Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>339388482</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>20208000636920909001</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Предоплата за материалы по договору №145/26</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>526274000</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B166" t="n">
+        <v>258</v>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>52708000</v>
+      </c>
+      <c r="D166" s="2" t="n"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Andijon Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>339388482</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>20208000636920909001</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Materiallar uchun oldindan to'lov, shartn. №12/26</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>473566000</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B167" t="n">
+        <v>259</v>
+      </c>
+      <c r="C167" s="2" t="n"/>
+      <c r="D167" s="2" t="n">
+        <v>8813000</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Chust Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>254875872</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>20208000600665421001</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №1368 23.09.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>482379000</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B168" t="n">
+        <v>260</v>
+      </c>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n">
+        <v>6773000</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Chust Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>254875872</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>20208000600665421001</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №156/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>489152000</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B169" t="n">
+        <v>261</v>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v>13046000</v>
+      </c>
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>НДС за август 2026 г.</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>476106000</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B170" t="n">
+        <v>262</v>
+      </c>
+      <c r="C170" s="2" t="n">
+        <v>16563000</v>
+      </c>
+      <c r="D170" s="2" t="n"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Oltin Vodiy Poligraf AJ</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>395119457</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>20208000775868982001</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Предоплата за материалы по дог. №156/26</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>459543000</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B171" t="n">
+        <v>263</v>
+      </c>
+      <c r="C171" s="2" t="n"/>
+      <c r="D171" s="2" t="n">
+        <v>19119000</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>288673440</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>20208000845286443001</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №9838 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>478662000</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B172" t="n">
+        <v>264</v>
+      </c>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n">
+        <v>13455000</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>288673440</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>20208000845286443001</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №9/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>492117000</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B173" t="n">
+        <v>265</v>
+      </c>
+      <c r="C173" s="2" t="n">
+        <v>27667000</v>
+      </c>
+      <c r="D173" s="2" t="n"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Andijon Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>339388482</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>20208000636920909001</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно с/ф №6800</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>464450000</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B174" t="n">
+        <v>266</v>
+      </c>
+      <c r="C174" s="2" t="n"/>
+      <c r="D174" s="2" t="n">
+        <v>12599000</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>288673440</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>20208000845286443001</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №118/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>477049000</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B175" t="n">
+        <v>267</v>
+      </c>
+      <c r="C175" s="2" t="n">
+        <v>4883000</v>
+      </c>
+      <c r="D175" s="2" t="n"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>20208000712740066001</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Оплата за электроэнергию согласно счету</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>472166000</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B176" t="n">
+        <v>268</v>
+      </c>
+      <c r="C176" s="2" t="n">
+        <v>228115000</v>
+      </c>
+      <c r="D176" s="2" t="n"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Chirchiq Agro MChJ</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>311692015</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>20208000914125098001</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Оплата за сырье по дог. №232/26 от 28.09.2026, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>244051000</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B177" t="n">
+        <v>269</v>
+      </c>
+      <c r="C177" s="2" t="n"/>
+      <c r="D177" s="2" t="n">
+        <v>8232000</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Chirchiq Avto Ehtiyot AJ</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>288673440</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>20208000845286443001</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Оплата за товар по с/ф №8650 от 29.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>252283000</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B178" t="n">
+        <v>270</v>
+      </c>
+      <c r="C178" s="2" t="n"/>
+      <c r="D178" s="2" t="n">
+        <v>28500000</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Ishonch Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>350761319</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>20208000574140165001</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Shartnoma №274/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v>280783000</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B179" t="n">
+        <v>271</v>
+      </c>
+      <c r="C179" s="2" t="n">
         <v>300000</v>
       </c>
-      <c r="D147" s="2" t="n"/>
-      <c r="E147" t="inlineStr">
+      <c r="D179" s="2" t="n"/>
+      <c r="E179" t="inlineStr">
         <is>
           <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="G179" t="inlineStr">
         <is>
           <t>45994000900000001001</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
+      <c r="H179" t="inlineStr">
         <is>
           <t>00987</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
-        </is>
-      </c>
-      <c r="J147" s="2" t="n">
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Bank xizmati uchun komissiya</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>280483000</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B180" t="n">
+        <v>272</v>
+      </c>
+      <c r="C180" s="2" t="n">
+        <v>23483000</v>
+      </c>
+      <c r="D180" s="2" t="n"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Nihol Un Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>284659880</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>20208000576757442001</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по договору №53/26</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="n">
         <v>257000000</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
+    <row r="181">
+      <c r="A181" t="inlineStr">
         <is>
           <t>Итого обороты:</t>
         </is>
       </c>
-      <c r="C148" s="4" t="n">
-        <v>3289397000</v>
-      </c>
-      <c r="D148" s="4" t="n">
-        <v>3279197000</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="C181" s="4" t="n">
+        <v>3200517000</v>
+      </c>
+      <c r="D181" s="4" t="n">
+        <v>3190317000</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
         <is>
           <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
-      <c r="C149" s="4" t="n">
+      <c r="C182" s="4" t="n">
         <v>257000000</v>
       </c>
-      <c r="D149" s="4" t="n"/>
+      <c r="D182" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
